--- a/光伏配储项目/电价数据/2026/宏阳站.xlsx
+++ b/光伏配储项目/电价数据/2026/宏阳站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51018</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74234</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5709500000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5768300000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49676</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43996</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41991</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11503</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10147</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08726</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11105</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04604999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09175</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.11366</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.11912</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.10997</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08976000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.06183</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15062</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21586</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13819</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18452</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5434099999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48098</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.9135700000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.58824</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5664199999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.59688</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79575</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63552</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6115499999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.72475</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.84246</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65937</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6176799999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6667799999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6055199999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.60049</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63324</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60323</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48773</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42583</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6869700000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.72284</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7740499999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.21517</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8375499999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52696</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51925</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5053799999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50731</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49011</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59742</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.68975</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5043500000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15462</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.04089</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48097</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77942</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9358099999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.78335</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10683</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26216</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25349</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5462100000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6720499999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5199600000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68602</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75958</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.81836</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.93504</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6088300000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.53254</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19634</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.43597</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26691</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14621</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.44982</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59597</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.52623</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.46616</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4606</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2739</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13099</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20197</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.15944</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.06544</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.05878</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.13047</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28309</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.15949</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50243</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05325999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12102</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23157</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22591</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21288</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14304</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41877</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5707000000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29714</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04418</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04701</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03583</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04651</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04178</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04179</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04081</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04670000000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21909</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05266</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10947</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35105</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67588</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04333</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03731</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10481</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00109</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04361</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04302</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04503</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04517</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04407</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20027</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14307</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33585</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31822</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17265</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17126</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15889</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23662</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45383</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15665</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62202</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92035</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49453</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9169400000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.87138</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.3008</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8958200000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6330399999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19526</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87279</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54818</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33922</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03867</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5391699999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7981</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53064</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78013</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7832100000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8776499999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8776</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49983</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40854</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21564</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8791599999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55122</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6304099999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54049</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45691</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58705</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6022799999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66711</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57885</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87679</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63303</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86341</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.84539</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86121</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35348</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92945</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46884</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50046</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16522</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19937</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20323</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44842</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59738</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89032</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.30652</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.11592</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6886100000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77536</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63913</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57275</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44617</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49412</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43557</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49446</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44598</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49448</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.19478</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56951</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5696599999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26232</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57543</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45932</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32432</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.09112000000000001</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23868</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15306</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15726</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16447</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14968</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.15487</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15352</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.15341</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.12011</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10927</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.15432</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14792</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15262</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43625</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34907</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5324099999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24067</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24005</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25123</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35907</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.00564</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.10842</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22076</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7114400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.53522</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2879</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3496</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.69223</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7723</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48035</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45593</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35103</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14748</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19924</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25774</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21823</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26185</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14986</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.60065</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6651</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.69389</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48784</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74021</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.53174</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.89198</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47076</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48292</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48354</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43047</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49104</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.50392</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.50669</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45697</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56041</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49366</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44574</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.59558</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44353</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52423</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46523</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6412</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15692</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48686</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50717</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5443300000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.61558</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.79267</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.8104199999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.88627</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.70213</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8049700000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.60427</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5585800000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9408300000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.86264</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63171</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.7119099999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50987</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49651</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5677300000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47026</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45738</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.47152</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41052</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18251</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11048</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18075</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42856</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41286</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3655</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44478</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27194</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22788</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25029</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13976</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25142</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16924</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18099</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22814</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23243</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35044</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25915</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24629</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20829</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02864</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10808</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01578</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03962</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0209</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04124</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04869</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04835</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02669</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03102</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.12819</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00281</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03355</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17073</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.14481</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5774600000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.16986</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26426</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25235</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24241</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25273</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25052</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23245</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.16718</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.64351</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.64228</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6613300000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5814199999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.16604</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09268999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23947</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.18076</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12649</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.08946999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04088</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02567</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.12533</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.13109</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01545</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.10859</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.11642</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27459</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32368</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48806</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.56232</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47179</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.46598</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13997</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33396</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6365299999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.6071599999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.53777</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.52673</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45815</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47162</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46772</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.44846</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48596</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.55736</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37669</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47858</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.47121</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45149</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.60366</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6023999999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5815900000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.56908</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.52747</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.57075</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.50212</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.06222</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9087499999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.61772</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.61002</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46524</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38095</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.13294</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.22441</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17535</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05853</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.14639</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02712</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19586</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16296</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00118</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15509</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05377000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05005</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06406999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14907</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07158</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05382</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16948</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14069</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.45048</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.56753</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38089</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.98341</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11373</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01829</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01762</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17108</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04065999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00561</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16335</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04493</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24141</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48333</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41584</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5710299999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.63185</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42866</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3752</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6150599999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25996</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23358</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21077</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23438</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11573</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15313</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04647999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07995000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02905</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06429</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09845999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17374</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19824</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12234</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12546</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14914</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11841</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23861</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18944</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24429</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20738</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5152899999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41374</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3831</v>
       </c>
     </row>
   </sheetData>
